--- a/reports/complex_models_metrics.xlsx
+++ b/reports/complex_models_metrics.xlsx
@@ -483,13 +483,13 @@
         <v>1.995164825341298</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5963603444410407</v>
+        <v>0.5963603444410405</v>
       </c>
       <c r="D2" t="n">
-        <v>3.185745408664587</v>
+        <v>3.185745408664586</v>
       </c>
       <c r="E2" t="n">
-        <v>1.149355908553005</v>
+        <v>1.149355908553004</v>
       </c>
       <c r="F2" t="n">
         <v>0.808528880805941</v>
@@ -504,10 +504,10 @@
         <v>2.723065105296889</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4372873840297378</v>
+        <v>0.4372873840297379</v>
       </c>
       <c r="K2" t="n">
-        <v>0.147</v>
+        <v>0.2703</v>
       </c>
     </row>
     <row r="3">
@@ -544,7 +544,7 @@
         <v>0.6981777499476238</v>
       </c>
       <c r="K3" t="n">
-        <v>0.027</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="4">
@@ -581,7 +581,7 @@
         <v>0.1687973855091928</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007</v>
+        <v>0.001</v>
       </c>
     </row>
   </sheetData>
